--- a/assets/downloads/AX1S-Maandelijks-Cost-Report-Template.xlsx
+++ b/assets/downloads/AX1S-Maandelijks-Cost-Report-Template.xlsx
@@ -8,8 +8,12 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Cost Report" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Introductie" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Cost Report" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Cost Report'!$A$6:$F$14</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -20,12 +24,69 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t xml:space="preserve">AX1S Infra — Maandelijks Cost Report Sjabloon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vul per team de kosten van vorige en deze maand in (blauwe cellen). Verandering (€/%) en de totalen berekenen zichzelf.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+  <si>
+    <t xml:space="preserve">Maandelijks Cost Report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Een sjabloon met werkende formules om cloud-, SaaS- en AI-kosten per team maandelijks te rapporteren aan je organisatie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoe gebruik je dit sjabloon?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ga naar het tabblad “Cost Report”.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vul de rapportmaand in en per team de kosten van vorige en deze maand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formules doen de rest.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verandering in euro's en procenten, en de totaalrij, berekenen zichzelf.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kijk naar de kleurmarkering.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rood = kosten gestegen, groen = kosten gedaald t.o.v. vorige maand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bekijk de grafiek onderaan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Een direct visueel overzicht van vorige maand vs. deze maand, per team.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kopieer dit tabblad elke maand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zo bouw je vanzelf een historisch overzicht op.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meer nodig dan dit sjabloon?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AX1S Infra helpt SaaS, fintech en digital-first bedrijven structureel besparen op cloud-, SaaS- en AI-kosten. Gratis intake: ax1s-infra.com/#contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blauwe cellen zijn voorbeelddata — vervang met jullie eigen cijfers. Zwarte cellen berekenen zichzelf.</t>
   </si>
   <si>
     <t xml:space="preserve">Rapportmaand:</t>
@@ -79,7 +140,7 @@
     <t xml:space="preserve">Totaal</t>
   </si>
   <si>
-    <t xml:space="preserve">Blauwe cellen zijn voorbeelddata — vervang met jullie eigen cijfers. Zwarte cellen berekenen zichzelf.</t>
+    <t xml:space="preserve">Rood = kosten gestegen t.o.v. vorige maand. Groen = kosten gedaald.</t>
   </si>
 </sst>
 </file>
@@ -91,7 +152,7 @@
     <numFmt numFmtId="165" formatCode="\€#,##0;[RED]&quot;-€&quot;#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0%;[RED]\-0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,31 +177,77 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="16"/>
+      <sz val="22"/>
       <color rgb="FF0B0D16"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
-      <sz val="10"/>
+      <sz val="12"/>
       <color rgb="FF555555"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="13"/>
+      <color rgb="FF0070F3"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF0070F3"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10.5"/>
+      <color rgb="FF222222"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
+      <color rgb="FF555555"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF0B0D16"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="15"/>
+      <color rgb="FF0B0D16"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10.5"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF0033CC"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -148,30 +255,52 @@
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10.5"/>
+      <color rgb="FF222222"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10.5"/>
+      <color rgb="FF0B0D16"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF9DB"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -182,7 +311,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEAF1FF"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF7F9FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF9DB"/>
+        <bgColor rgb="FFF9F9F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF9F9F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F9FC"/>
+        <bgColor rgb="FFF9F9F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E7FF"/>
+        <bgColor rgb="FFD5DCE8"/>
       </patternFill>
     </fill>
   </fills>
@@ -196,16 +349,16 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="FFD5DCE8"/>
       </left>
       <right style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="FFD5DCE8"/>
       </right>
       <top style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="FFD5DCE8"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="FFD5DCE8"/>
       </bottom>
       <diagonal/>
     </border>
@@ -235,16 +388,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -252,63 +405,99 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -321,6 +510,99 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0070F3"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF9DB"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0033CC"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF7F9FC"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1B8A5A"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF222222"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC0392B"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFC0392B"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF1B8A5A"/>
+      </font>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -337,8 +619,8 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FFB7C0CD"/>
+      <rgbColor rgb="FF878787"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF9DB"/>
@@ -346,7 +628,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0070F3"/>
-      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FFD5DCE8"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -356,13 +638,13 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFD9E7FF"/>
+      <rgbColor rgb="FFF7F9FC"/>
+      <rgbColor rgb="FFF9F9F9"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -372,16 +654,739 @@
       <rgbColor rgb="FF555555"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF1B8A5A"/>
       <rgbColor rgb="FF0B0D16"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FFC0392B"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="FF0033CC"/>
+      <rgbColor rgb="FF222222"/>
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="10"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1800" b="1" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:uFillTx/>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Kosten per team: vorige maand vs. deze maand</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Cost Report'!B6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Vorige maand (€)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="B7C0CD"/>
+            </a:solidFill>
+            <a:ln w="12600">
+              <a:solidFill>
+                <a:srgbClr val="F9F9F9"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="0">
+                  <a:solidFill>
+                    <a:srgbClr val="F9F9F9"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Cost Report'!$A$7:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Platform</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Growth</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Data</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>AI/ML</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Cost Report'!$B$7:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>\€#,##0;[RED]"-€"#,##0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>18400</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12600</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7300</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Cost Report'!C6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Deze maand (€)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="0070F3"/>
+            </a:solidFill>
+            <a:ln w="12600">
+              <a:solidFill>
+                <a:srgbClr val="F9F9F9"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="0">
+                  <a:solidFill>
+                    <a:srgbClr val="F9F9F9"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Cost Report'!$A$7:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Platform</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Growth</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Data</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>AI/ML</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Cost Report'!$C$7:$C$10</c:f>
+              <c:numCache>
+                <c:formatCode>\€#,##0;[RED]"-€"#,##0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12050</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9800</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="150"/>
+        <c:overlap val="0"/>
+        <c:axId val="61612736"/>
+        <c:axId val="11246146"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="61612736"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:uFillTx/>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="11246146"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="11246146"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="1000" b="1" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Euro</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="\€#,##0;[RED]&quot;-€&quot;#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:uFillTx/>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="61612736"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarkerLayout>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1238040</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>50040</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="211320" y="285840"/>
+          <a:ext cx="1238040" cy="430920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>699840</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>21960</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="3705120"/>
+        <a:ext cx="6479640" cy="2879640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -562,253 +1567,471 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <tabColor rgb="FF0070F3"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="3"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="26.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="C13" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C14" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C17" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="8" t="n">
-        <v>18400</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>16200</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <f aca="false">C6-B6</f>
-        <v>-2200</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <f aca="false">IFERROR((C6-B6)/B6,0)</f>
-        <v>-0.119565217391304</v>
-      </c>
-      <c r="F6" s="7" t="s">
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C20" s="7" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="8" t="n">
-        <v>9200</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>10100</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <f aca="false">C7-B7</f>
-        <v>900</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <f aca="false">IFERROR((C7-B7)/B7,0)</f>
-        <v>0.0978260869565217</v>
-      </c>
-      <c r="F7" s="7" t="s">
+      <c r="C22" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C23" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>12600</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>12050</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <f aca="false">C8-B8</f>
-        <v>-550</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <f aca="false">IFERROR((C8-B8)/B8,0)</f>
-        <v>-0.0436507936507937</v>
-      </c>
-      <c r="F8" s="7" t="s">
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="C25" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>7300</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>9800</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <f aca="false">C9-B9</f>
-        <v>2500</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <f aca="false">IFERROR((C9-B9)/B9,0)</f>
-        <v>0.342465753424658</v>
-      </c>
-      <c r="F9" s="7" t="s">
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C26" s="7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="12" t="str">
-        <f aca="false">IF(AND(B10="",C10=""),"",C10-B10)</f>
-        <v/>
-      </c>
-      <c r="E10" s="13" t="str">
-        <f aca="false">IF(OR(B10="",B10=0),"",(C10-B10)/B10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="11"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="12" t="str">
-        <f aca="false">IF(AND(B11="",C11=""),"",C11-B11)</f>
-        <v/>
-      </c>
-      <c r="E11" s="13" t="str">
-        <f aca="false">IF(OR(B11="",B11=0),"",(C11-B11)/B11)</f>
-        <v/>
-      </c>
-      <c r="F11" s="11"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="12" t="str">
-        <f aca="false">IF(AND(B12="",C12=""),"",C12-B12)</f>
-        <v/>
-      </c>
-      <c r="E12" s="13" t="str">
-        <f aca="false">IF(OR(B12="",B12=0),"",(C12-B12)/B12)</f>
-        <v/>
-      </c>
-      <c r="F12" s="11"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="12" t="str">
-        <f aca="false">IF(AND(B13="",C13=""),"",C13-B13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="13" t="str">
-        <f aca="false">IF(OR(B13="",B13=0),"",(C13-B13)/B13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="11"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="15" t="n">
-        <f aca="false">SUM(B6:B13)</f>
-        <v>47500</v>
-      </c>
-      <c r="C14" s="15" t="n">
-        <f aca="false">SUM(C6:C13)</f>
-        <v>48150</v>
-      </c>
-      <c r="D14" s="15" t="n">
-        <f aca="false">C14-B14</f>
-        <v>650</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <f aca="false">IFERROR((C14-B14)/B14,0)</f>
-        <v>0.0136842105263158</v>
-      </c>
-      <c r="F14" s="17"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
+  <mergeCells count="15">
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:F9"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF0070F3"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>18400</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>16200</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <f aca="false">C7-B7</f>
+        <v>-2200</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <f aca="false">IFERROR((C7-B7)/B7,0)</f>
+        <v>-0.119565217391304</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>9200</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>10100</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <f aca="false">C8-B8</f>
+        <v>900</v>
+      </c>
+      <c r="E8" s="20" t="n">
+        <f aca="false">IFERROR((C8-B8)/B8,0)</f>
+        <v>0.0978260869565217</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>12600</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>12050</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <f aca="false">C9-B9</f>
+        <v>-550</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <f aca="false">IFERROR((C9-B9)/B9,0)</f>
+        <v>-0.0436507936507937</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="16" t="n">
+        <v>7300</v>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>9800</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <f aca="false">C10-B10</f>
+        <v>2500</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <f aca="false">IFERROR((C10-B10)/B10,0)</f>
+        <v>0.342465753424658</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="22" t="str">
+        <f aca="false">IF(AND(B11="",C11=""),"",C11-B11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="23" t="str">
+        <f aca="false">IF(OR(B11="",B11=0),"",(C11-B11)/B11)</f>
+        <v/>
+      </c>
+      <c r="F11" s="21"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="22" t="str">
+        <f aca="false">IF(AND(B12="",C12=""),"",C12-B12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="23" t="str">
+        <f aca="false">IF(OR(B12="",B12=0),"",(C12-B12)/B12)</f>
+        <v/>
+      </c>
+      <c r="F12" s="21"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="22" t="str">
+        <f aca="false">IF(AND(B13="",C13=""),"",C13-B13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="23" t="str">
+        <f aca="false">IF(OR(B13="",B13=0),"",(C13-B13)/B13)</f>
+        <v/>
+      </c>
+      <c r="F13" s="21"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="22" t="str">
+        <f aca="false">IF(AND(B14="",C14=""),"",C14-B14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="23" t="str">
+        <f aca="false">IF(OR(B14="",B14=0),"",(C14-B14)/B14)</f>
+        <v/>
+      </c>
+      <c r="F14" s="21"/>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="25" t="n">
+        <f aca="false">SUM(B7:B14)</f>
+        <v>47500</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <f aca="false">SUM(C7:C14)</f>
+        <v>48150</v>
+      </c>
+      <c r="D15" s="25" t="n">
+        <f aca="false">C15-B15</f>
+        <v>650</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <f aca="false">IFERROR((C15-B15)/B15,0)</f>
+        <v>0.0136842105263158</v>
+      </c>
+      <c r="F15" s="27"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:F14"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A17:F17"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D7:D14">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7:E14">
+    <cfRule type="cellIs" priority="4" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>